--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484159_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484159_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D. FERNANDEZ STEFANUTO</t>
+          <t>A. DUCH BELTRAN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.5833</v>
+        <v>7.2482</v>
       </c>
       <c r="E2" t="n">
-        <v>7.1383</v>
+        <v>5.2938</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4449</v>
+        <v>1.9544</v>
       </c>
       <c r="G2" t="n">
-        <v>5.294</v>
+        <v>2.183</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3527</v>
+        <v>0.5896</v>
       </c>
       <c r="I2" t="n">
-        <v>4.9413</v>
+        <v>1.5935</v>
       </c>
       <c r="J2" t="n">
-        <v>6.3714</v>
+        <v>1.6063</v>
       </c>
       <c r="K2" t="n">
-        <v>1.8708</v>
+        <v>1.1142</v>
       </c>
       <c r="L2" t="n">
-        <v>4.5007</v>
+        <v>0.4921</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.0774</v>
+        <v>0.5767</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.518</v>
+        <v>-0.5246</v>
       </c>
       <c r="O2" t="n">
-        <v>0.4406</v>
+        <v>1.1013</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.5952</v>
+        <v>2.1822</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.9838</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.3887</v>
+        <v>2.1822</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0747</v>
+        <v>-0.4705</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9411</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1337</v>
+        <v>-0.5386</v>
       </c>
       <c r="V2" t="n">
-        <v>1.8097</v>
+        <v>3.3534</v>
       </c>
       <c r="W2" t="n">
-        <v>1.8097</v>
+        <v>3.6194</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. DUCH BELTRAN</t>
+          <t>D. FERNANDEZ STEFANUTO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.9614</v>
+        <v>7.2284</v>
       </c>
       <c r="E3" t="n">
-        <v>5.2315</v>
+        <v>6.4468</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7299</v>
+        <v>0.7816</v>
       </c>
       <c r="G3" t="n">
-        <v>2.183</v>
+        <v>5.294</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5896</v>
+        <v>0.3527</v>
       </c>
       <c r="I3" t="n">
-        <v>1.5935</v>
+        <v>4.9413</v>
       </c>
       <c r="J3" t="n">
-        <v>1.6063</v>
+        <v>6.3714</v>
       </c>
       <c r="K3" t="n">
-        <v>1.1142</v>
+        <v>1.8708</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4921</v>
+        <v>4.5007</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5767</v>
+        <v>-1.0774</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.5246</v>
+        <v>-1.518</v>
       </c>
       <c r="O3" t="n">
-        <v>1.1013</v>
+        <v>0.4406</v>
       </c>
       <c r="P3" t="n">
-        <v>2.1822</v>
+        <v>-0.5952</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.9838</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1822</v>
+        <v>1.3887</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7572</v>
+        <v>0.7198</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0057</v>
+        <v>0.2495</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.763</v>
+        <v>0.4703</v>
       </c>
       <c r="V3" t="n">
-        <v>3.3534</v>
+        <v>1.8097</v>
       </c>
       <c r="W3" t="n">
-        <v>3.6194</v>
+        <v>1.8097</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.266</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.6055</v>
+        <v>3.6244</v>
       </c>
       <c r="E4" t="n">
-        <v>3.433</v>
+        <v>3.0873</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1725</v>
+        <v>0.5372</v>
       </c>
       <c r="G4" t="n">
         <v>3.5781</v>
@@ -766,13 +766,13 @@
         <v>0.7935</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2772</v>
+        <v>0.2961</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0056</v>
+        <v>-0.3514</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2828</v>
+        <v>0.6475</v>
       </c>
       <c r="V4" t="n">
         <v>0.9405</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. BUSCAIL BRIANSO</t>
+          <t>D. FERNANDEZ LINARES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.067</v>
+        <v>3.5543</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1912</v>
+        <v>2.5702</v>
       </c>
       <c r="F5" t="n">
-        <v>3.2582</v>
+        <v>0.9842</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.2825</v>
+        <v>3.6582</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.6624</v>
+        <v>-0.3786</v>
       </c>
       <c r="I5" t="n">
-        <v>1.3799</v>
+        <v>4.0368</v>
       </c>
       <c r="J5" t="n">
-        <v>0.331</v>
+        <v>4.288</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.4722</v>
+        <v>0.1411</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8032</v>
+        <v>4.1469</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.6135</v>
+        <v>-0.6298</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.1902</v>
+        <v>-0.5197000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5767</v>
+        <v>-0.11</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.9919</v>
+        <v>-1.5871</v>
       </c>
       <c r="Q5" t="n">
         <v>-1.9838</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9919</v>
+        <v>0.3968</v>
       </c>
       <c r="S5" t="n">
-        <v>3.135</v>
+        <v>0.5427</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9297</v>
+        <v>0.0001</v>
       </c>
       <c r="U5" t="n">
-        <v>2.2053</v>
+        <v>0.5426</v>
       </c>
       <c r="V5" t="n">
-        <v>1.2065</v>
+        <v>0.9405</v>
       </c>
       <c r="W5" t="n">
-        <v>0.532</v>
+        <v>0.266</v>
       </c>
       <c r="X5" t="n">
         <v>0.6745</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. ISSOUF</t>
+          <t>I. FERNANDEZ MASIP</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4027</v>
+        <v>2.5051</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5217000000000001</v>
+        <v>2.3973</v>
       </c>
       <c r="F6" t="n">
-        <v>1.881</v>
+        <v>0.1079</v>
       </c>
       <c r="G6" t="n">
-        <v>2.4048</v>
+        <v>2.0315</v>
       </c>
       <c r="H6" t="n">
-        <v>1.4616</v>
+        <v>-0.1256</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9432</v>
+        <v>2.1571</v>
       </c>
       <c r="J6" t="n">
-        <v>2.0411</v>
+        <v>2.2564</v>
       </c>
       <c r="K6" t="n">
-        <v>1.9207</v>
+        <v>1.6087</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1205</v>
+        <v>0.6477000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3637</v>
+        <v>-0.2249</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.459</v>
+        <v>-1.7343</v>
       </c>
       <c r="O6" t="n">
-        <v>0.8227</v>
+        <v>1.5094</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.7935</v>
+        <v>2.1822</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9838</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1903</v>
+        <v>2.1822</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5255</v>
+        <v>-0.4308</v>
       </c>
       <c r="T6" t="n">
-        <v>0.873</v>
+        <v>-0.391</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3475</v>
+        <v>-0.0398</v>
       </c>
       <c r="V6" t="n">
-        <v>0.266</v>
+        <v>-1.2777</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.4085</v>
+        <v>0.532</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6745</v>
+        <v>-1.8097</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. FERNANDEZ LINARES</t>
+          <t>M. BUSCAIL BRIANSO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.3468</v>
+        <v>1.9343</v>
       </c>
       <c r="E7" t="n">
-        <v>1.8957</v>
+        <v>-0.6787</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4511</v>
+        <v>2.6129</v>
       </c>
       <c r="G7" t="n">
-        <v>3.6582</v>
+        <v>-0.2825</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3786</v>
+        <v>-1.6624</v>
       </c>
       <c r="I7" t="n">
-        <v>4.0368</v>
+        <v>1.3799</v>
       </c>
       <c r="J7" t="n">
-        <v>4.288</v>
+        <v>0.331</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1411</v>
+        <v>-0.4722</v>
       </c>
       <c r="L7" t="n">
-        <v>4.1469</v>
+        <v>0.8032</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.6298</v>
+        <v>-0.6135</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5197000000000001</v>
+        <v>-1.1902</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.11</v>
+        <v>0.5767</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.5871</v>
+        <v>-0.9919</v>
       </c>
       <c r="Q7" t="n">
         <v>-1.9838</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3968</v>
+        <v>0.9919</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6649</v>
+        <v>2.0022</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6744</v>
+        <v>0.4422</v>
       </c>
       <c r="U7" t="n">
-        <v>0.009599999999999999</v>
+        <v>1.56</v>
       </c>
       <c r="V7" t="n">
-        <v>0.9405</v>
+        <v>1.2065</v>
       </c>
       <c r="W7" t="n">
-        <v>0.266</v>
+        <v>0.532</v>
       </c>
       <c r="X7" t="n">
         <v>0.6745</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. FERNANDEZ MASIP</t>
+          <t>M. ISSOUF</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.2591</v>
+        <v>1.8248</v>
       </c>
       <c r="E8" t="n">
-        <v>1.9268</v>
+        <v>-0.0281</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3323</v>
+        <v>1.8529</v>
       </c>
       <c r="G8" t="n">
-        <v>2.0315</v>
+        <v>2.4048</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1256</v>
+        <v>1.4616</v>
       </c>
       <c r="I8" t="n">
-        <v>2.1571</v>
+        <v>0.9432</v>
       </c>
       <c r="J8" t="n">
-        <v>2.2564</v>
+        <v>2.0411</v>
       </c>
       <c r="K8" t="n">
-        <v>1.6087</v>
+        <v>1.9207</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6477000000000001</v>
+        <v>0.1205</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2249</v>
+        <v>0.3637</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.7343</v>
+        <v>-0.459</v>
       </c>
       <c r="O8" t="n">
-        <v>1.5094</v>
+        <v>0.8227</v>
       </c>
       <c r="P8" t="n">
-        <v>2.1822</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.9838</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1822</v>
+        <v>1.1903</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6768</v>
+        <v>-0.0524</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8615</v>
+        <v>0.3231</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1846</v>
+        <v>-0.3756</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.2777</v>
+        <v>0.266</v>
       </c>
       <c r="W8" t="n">
-        <v>0.532</v>
+        <v>-0.4085</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.8097</v>
+        <v>0.6745</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3251</v>
+        <v>0.9296</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1436</v>
+        <v>0.2645</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4687</v>
+        <v>0.665</v>
       </c>
       <c r="G9" t="n">
         <v>0.0581</v>
@@ -1156,13 +1156,13 @@
         <v>0.7935</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5266</v>
+        <v>0.0779</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2494</v>
+        <v>0.1587</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2772</v>
+        <v>-0.0808</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. ROSET CLAVERO</t>
+          <t>T. KOHAN LÓPEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,40 +1189,40 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5079</v>
+        <v>0.0439</v>
       </c>
       <c r="E10" t="n">
-        <v>1.223</v>
+        <v>1.0762</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.7309</v>
+        <v>-1.0323</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7526</v>
+        <v>-0.6359</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.09080000000000001</v>
+        <v>-0.7564</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8434</v>
+        <v>0.1205</v>
       </c>
       <c r="J10" t="n">
-        <v>1.2853</v>
+        <v>0.6855</v>
       </c>
       <c r="K10" t="n">
         <v>0.0403</v>
       </c>
       <c r="L10" t="n">
-        <v>1.245</v>
+        <v>0.6451</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.5328000000000001</v>
+        <v>-1.3213</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1312</v>
+        <v>-0.7967</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4016</v>
+        <v>-0.5247000000000001</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -1234,28 +1234,28 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.212</v>
+        <v>0.4138</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0623</v>
+        <v>0.1248</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2743</v>
+        <v>0.289</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.4724</v>
+        <v>0.266</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.4724</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>T. KOHAN LÓPEZ</t>
+          <t>J. ROSET CLAVERO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,40 +1267,40 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.6805</v>
+        <v>-0.5639999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>0.464</v>
+        <v>1.223</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1445</v>
+        <v>-1.787</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.6359</v>
+        <v>0.7526</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.7564</v>
+        <v>-0.09080000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1205</v>
+        <v>0.8434</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6855</v>
+        <v>1.2853</v>
       </c>
       <c r="K11" t="n">
         <v>0.0403</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6451</v>
+        <v>1.245</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.3213</v>
+        <v>-0.5328000000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7967</v>
+        <v>-0.1312</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.5247000000000001</v>
+        <v>-0.4016</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -1312,22 +1312,22 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3106</v>
+        <v>0.1559</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4874</v>
+        <v>-0.0623</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1768</v>
+        <v>0.2182</v>
       </c>
       <c r="V11" t="n">
-        <v>0.266</v>
+        <v>-1.4724</v>
       </c>
       <c r="W11" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.4724</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.1659</v>
+        <v>-3.0574</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.0215</v>
+        <v>-2.9592</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8557</v>
+        <v>-0.0982</v>
       </c>
       <c r="G12" t="n">
         <v>-2.0148</v>
@@ -1390,13 +1390,13 @@
         <v>1.7855</v>
       </c>
       <c r="S12" t="n">
-        <v>1.3251</v>
+        <v>0.4335</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.306</v>
+        <v>-0.2436</v>
       </c>
       <c r="U12" t="n">
-        <v>1.6311</v>
+        <v>0.6772</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2777</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.7697</v>
+        <v>-3.2213</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.0229</v>
+        <v>-3.6147</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2532</v>
+        <v>0.3934</v>
       </c>
       <c r="G13" t="n">
         <v>-3.5288</v>
@@ -1468,13 +1468,13 @@
         <v>1.1903</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4393</v>
+        <v>0.1091</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6121</v>
+        <v>-0.204</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1728</v>
+        <v>0.3131</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>21.4269</v>
+        <v>22.0503</v>
       </c>
       <c r="E14" t="n">
-        <v>14.4548</v>
+        <v>15.0784</v>
       </c>
       <c r="F14" t="n">
-        <v>6.972099999999998</v>
+        <v>6.971999999999999</v>
       </c>
       <c r="G14" t="n">
         <v>13.4983</v>
@@ -1519,7 +1519,7 @@
         <v>15.5145</v>
       </c>
       <c r="J14" t="n">
-        <v>20.1075</v>
+        <v>20.10750000000001</v>
       </c>
       <c r="K14" t="n">
         <v>8.901900000000001</v>
@@ -1537,7 +1537,7 @@
         <v>4.308699999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>-9.999999999998899e-05</v>
+        <v>-0.000100000000000211</v>
       </c>
       <c r="Q14" t="n">
         <v>-12.8947</v>
@@ -1546,13 +1546,13 @@
         <v>12.8949</v>
       </c>
       <c r="S14" t="n">
-        <v>3.1741</v>
+        <v>3.797300000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5092</v>
+        <v>0.1141999999999998</v>
       </c>
       <c r="U14" t="n">
-        <v>3.6833</v>
+        <v>3.6831</v>
       </c>
       <c r="V14" t="n">
         <v>4.7548</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. AGUILO RODRIGUEZ</t>
+          <t>C. POYATOS PARRA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.4389</v>
+        <v>1.9468</v>
       </c>
       <c r="E15" t="n">
-        <v>3.8677</v>
+        <v>3.6549</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4288</v>
+        <v>-1.7081</v>
       </c>
       <c r="G15" t="n">
-        <v>1.7464</v>
+        <v>0.9563</v>
       </c>
       <c r="H15" t="n">
-        <v>2.0612</v>
+        <v>1.8048</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3148</v>
+        <v>-0.8485</v>
       </c>
       <c r="J15" t="n">
-        <v>3.0975</v>
+        <v>4.5317</v>
       </c>
       <c r="K15" t="n">
-        <v>2.3695</v>
+        <v>3.1261</v>
       </c>
       <c r="L15" t="n">
-        <v>0.728</v>
+        <v>1.4057</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.3511</v>
+        <v>-3.5755</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3083</v>
+        <v>-1.3213</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.0428</v>
+        <v>-2.2542</v>
       </c>
       <c r="P15" t="n">
-        <v>0.5952</v>
+        <v>0.1984</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5871</v>
+        <v>2.1822</v>
       </c>
       <c r="S15" t="n">
-        <v>2.1092</v>
+        <v>0.1176</v>
       </c>
       <c r="T15" t="n">
-        <v>1.9047</v>
+        <v>-0.7027</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2045</v>
+        <v>0.8203</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.0118</v>
+        <v>0.6745</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.1425</v>
+        <v>1.8097</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.8692</v>
+        <v>-1.1352</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C. POYATOS PARRA</t>
+          <t>M. AGUILO RODRIGUEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4339</v>
+        <v>1.8923</v>
       </c>
       <c r="E16" t="n">
-        <v>3.5529</v>
+        <v>2.1332</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.1189</v>
+        <v>-0.2409</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9563</v>
+        <v>1.7464</v>
       </c>
       <c r="H16" t="n">
-        <v>1.8048</v>
+        <v>2.0612</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8485</v>
+        <v>-0.3148</v>
       </c>
       <c r="J16" t="n">
-        <v>4.5317</v>
+        <v>3.0975</v>
       </c>
       <c r="K16" t="n">
-        <v>3.1261</v>
+        <v>2.3695</v>
       </c>
       <c r="L16" t="n">
-        <v>1.4057</v>
+        <v>0.728</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.5755</v>
+        <v>-1.3511</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.3213</v>
+        <v>-0.3083</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.2542</v>
+        <v>-1.0428</v>
       </c>
       <c r="P16" t="n">
-        <v>0.1984</v>
+        <v>0.5952</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R16" t="n">
-        <v>2.1822</v>
+        <v>1.5871</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6047</v>
+        <v>0.5626</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8047</v>
+        <v>0.1702</v>
       </c>
       <c r="U16" t="n">
-        <v>1.4095</v>
+        <v>0.3924</v>
       </c>
       <c r="V16" t="n">
-        <v>0.6745</v>
+        <v>-1.0118</v>
       </c>
       <c r="W16" t="n">
-        <v>1.8097</v>
+        <v>-0.1425</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.1352</v>
+        <v>-0.8692</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. OCHOGAVIA CIFRE</t>
+          <t>A. ELLENA VICENTE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1925</v>
+        <v>0.7907999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>0.883</v>
+        <v>2.2044</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.6905</v>
+        <v>-1.4136</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.5886</v>
+        <v>3.086</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0255</v>
+        <v>2.6908</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.614</v>
+        <v>0.3951</v>
       </c>
       <c r="J17" t="n">
-        <v>0.923</v>
+        <v>4.5797</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8828</v>
+        <v>3.4073</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0402</v>
+        <v>1.1723</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.5116</v>
+        <v>-1.4937</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8574000000000001</v>
+        <v>-0.7165</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6542</v>
+        <v>-0.7772</v>
       </c>
       <c r="P17" t="n">
-        <v>1.3887</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.9838</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3887</v>
+        <v>1.1903</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6076</v>
+        <v>-0.5611</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.306</v>
+        <v>-0.6574</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3016</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.9405</v>
       </c>
       <c r="W17" t="n">
         <v>0.266</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.266</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. ELLENA VICENTE</t>
+          <t>M. OCHOGAVIA CIFRE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3077</v>
+        <v>-0.0218</v>
       </c>
       <c r="E18" t="n">
-        <v>1.4902</v>
+        <v>0.781</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.7979</v>
+        <v>-0.8027</v>
       </c>
       <c r="G18" t="n">
-        <v>3.086</v>
+        <v>-0.5886</v>
       </c>
       <c r="H18" t="n">
-        <v>2.6908</v>
+        <v>0.0255</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3951</v>
+        <v>-0.614</v>
       </c>
       <c r="J18" t="n">
-        <v>4.5797</v>
+        <v>0.923</v>
       </c>
       <c r="K18" t="n">
-        <v>3.4073</v>
+        <v>0.8828</v>
       </c>
       <c r="L18" t="n">
-        <v>1.1723</v>
+        <v>0.0402</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.4937</v>
+        <v>-1.5116</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7165</v>
+        <v>-0.8574000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.7772</v>
+        <v>-0.6542</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.7935</v>
+        <v>1.3887</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9838</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1903</v>
+        <v>1.3887</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.6596</v>
+        <v>-0.8219</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.3716</v>
+        <v>-0.408</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2881</v>
+        <v>-0.4139</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.9405</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0.266</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2065</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6468</v>
+        <v>-1.7572</v>
       </c>
       <c r="E19" t="n">
-        <v>0.631</v>
+        <v>-0.6954</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2778</v>
+        <v>-1.0618</v>
       </c>
       <c r="G19" t="n">
         <v>-1.1974</v>
@@ -1936,13 +1936,13 @@
         <v>0.3968</v>
       </c>
       <c r="S19" t="n">
-        <v>1.6064</v>
+        <v>0.496</v>
       </c>
       <c r="T19" t="n">
-        <v>1.9726</v>
+        <v>0.6463</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3662</v>
+        <v>-0.1503</v>
       </c>
       <c r="V19" t="n">
         <v>-0.4607</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.2787</v>
+        <v>-2.4259</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.4732</v>
+        <v>-1.0651</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.8055</v>
+        <v>-1.3608</v>
       </c>
       <c r="G20" t="n">
         <v>-2.261</v>
@@ -2014,13 +2014,13 @@
         <v>0.9919</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8031</v>
+        <v>0.0496</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9352</v>
+        <v>-0.5271</v>
       </c>
       <c r="U20" t="n">
-        <v>0.132</v>
+        <v>0.5767</v>
       </c>
       <c r="V20" t="n">
         <v>-1.2065</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.7348</v>
+        <v>-2.7239</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.6259</v>
+        <v>-1.1158</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.1089</v>
+        <v>-1.6081</v>
       </c>
       <c r="G21" t="n">
         <v>0.1977</v>
@@ -2092,13 +2092,13 @@
         <v>0.9919</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.5196</v>
+        <v>-0.5087</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.1222</v>
+        <v>-0.6121</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3974</v>
+        <v>0.1034</v>
       </c>
       <c r="V21" t="n">
         <v>-2.4129</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.6677</v>
+        <v>-3.6389</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.4278</v>
+        <v>-1.8156</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.2399</v>
+        <v>-1.8233</v>
       </c>
       <c r="G22" t="n">
         <v>-5.2624</v>
@@ -2170,13 +2170,13 @@
         <v>1.5871</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.6154</v>
+        <v>-0.5866</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.1109</v>
+        <v>-0.4987</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5044999999999999</v>
+        <v>-0.08790000000000001</v>
       </c>
       <c r="V22" t="n">
         <v>1.615</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.5227</v>
+        <v>-5.3509</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.1489</v>
+        <v>-3.9449</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.3737</v>
+        <v>-1.406</v>
       </c>
       <c r="G23" t="n">
         <v>-3.4776</v>
@@ -2248,13 +2248,13 @@
         <v>0.5952</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6564</v>
+        <v>-0.4846</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4874</v>
+        <v>-0.2834</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.169</v>
+        <v>-0.2013</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-9.3338</v>
+        <v>-8.777699999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.7209</v>
+        <v>-7.1087</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.6129</v>
+        <v>-1.6691</v>
       </c>
       <c r="G24" t="n">
         <v>-6.6976</v>
@@ -2326,13 +2326,13 @@
         <v>1.9838</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6326000000000001</v>
+        <v>-0.0765</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.4226</v>
+        <v>-0.8104</v>
       </c>
       <c r="U24" t="n">
-        <v>0.79</v>
+        <v>0.7339</v>
       </c>
       <c r="V24" t="n">
         <v>-1.0118</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-21.4269</v>
+        <v>-20.0664</v>
       </c>
       <c r="E25" t="n">
-        <v>-6.9719</v>
+        <v>-6.972</v>
       </c>
       <c r="F25" t="n">
-        <v>-14.4548</v>
+        <v>-13.0944</v>
       </c>
       <c r="G25" t="n">
         <v>-13.4982</v>
@@ -2404,13 +2404,13 @@
         <v>12.895</v>
       </c>
       <c r="S25" t="n">
-        <v>-3.174</v>
+        <v>-1.8136</v>
       </c>
       <c r="T25" t="n">
         <v>-3.6833</v>
       </c>
       <c r="U25" t="n">
-        <v>0.5091999999999999</v>
+        <v>1.8695</v>
       </c>
       <c r="V25" t="n">
         <v>-4.7547</v>
